--- a/光伏配储项目/电价数据/2026/双铁站.xlsx
+++ b/光伏配储项目/电价数据/2026/双铁站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51161</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7627699999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57486</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6040099999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51902</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4090299999999999</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44451</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13079</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10626</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12183</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11156</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13456</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05012</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11188</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.16403</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.16302</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09157</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06945999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10344</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15341</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21717</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25798</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.12703</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14448</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.2161</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6609299999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55975</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5833700000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.37794</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.62815</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.44534</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58104</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48099</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6439</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82869</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6428400000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6579299999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8096599999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.21095</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6932699999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60278</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.84977</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.67135</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65654</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6271</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.48009</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48077</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42589</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7122000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77583</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7978500000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.85642</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5354099999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51835</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5050899999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51045</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48799</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.60054</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.74451</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5254099999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17707</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06798</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5082300000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7705700000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.22683</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.54183</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.52395</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.46766</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.44389</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6534099999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7977000000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6404</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.69859</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.74441</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.6804</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.60924</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7763099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.59136</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45983</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06887</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66938</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33462</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51734</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5350900000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45446</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44859</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47947</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41054</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.51789</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49124</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17006</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28516</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.52203</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.52307</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.67648</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57353</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6476000000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.74549</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57598</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.50607</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44939</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5386</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.49243</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47699</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46279</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34236</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43374</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46074</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.19555</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.18321</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26736</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5206799999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45303</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.10636</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.10447</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17722</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.18836</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.53261</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07218000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.13021</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.23911</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25194</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21882</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23798</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20266</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26664</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12305</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.25858</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6639299999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29978</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41363</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03997</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05157</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03598</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04704</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04834</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04557</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04592</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04775</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04667</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04193</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04449</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04046</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04631</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05520000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04973</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04754</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00373</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01842</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15845</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05812</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11508</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46734</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35063</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6800499999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04378</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09897</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00412</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04385</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04361</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04417</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04837</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04769</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20003</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14291</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33544</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31763</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17248</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15873</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17101</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14777</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23626</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21408</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22663</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45612</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50774</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909299999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62209</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810900000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92055</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91561</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86624</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29853</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89138</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63242</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19095</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8707</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5410499999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33473</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03562</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5346000000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79415</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52952</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77618</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78007</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87717</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8755299999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49612</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40377</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45336</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21087</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87902</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55113</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49884</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45634</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58563</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59568</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6017400000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66254</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47488</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45226</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8800800000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6306900000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87915</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8616900000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86586</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45156</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91831</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16645</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19901</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19329</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5949</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88993</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33069</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13822</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69816</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78842</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64432</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57751</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43666</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49913</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4939</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.11937</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6294299999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25046</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.13167</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6994400000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.77322</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26059</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5774400000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46183</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74907</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32343</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42126</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.37121</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>1.18306</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1.16513</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>1.15262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.16347</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.28855</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>1.16824</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>1.29732</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>1.16249</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23241</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1.13541</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.13768</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.21319</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16124</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16642</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3484</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5366599999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46706</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20288</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24963</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24141</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2426</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.46816</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35981</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.51613</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.78283</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.5345299999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.7299</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12585</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70812</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5325299999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28452</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34941</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6524800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7730399999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4574</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34373</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20131</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26245</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22394</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28145</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.88059</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.78943</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7831699999999999</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.5589500000000001</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.78774</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.77507</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6475299999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60558</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5848300000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67186</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82504</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.03781</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47645</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35976</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48951</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48517</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49409</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55749</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49873</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44931</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47445</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44912</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6902999999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46729</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65483</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.25057</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49366</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51045</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51069</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54512</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6959099999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7288300000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67108</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81177</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59234</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5241</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83139</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62812</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67513</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48205</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47651</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46813</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55649</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45486</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41537</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21056</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11856</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18021</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1.18061</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43096</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43949</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36471</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22623</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23087</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25065</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13923</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17176</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18371</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22932</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23279</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27578</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3494</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20151</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24944</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03082</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04884</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11432</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01898</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03882</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00825</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03371</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02929</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02251</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.18993</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00121</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04895</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03379</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04293</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18296</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19228</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23261</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26643</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28065</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12359</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.56348</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.14479</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26358</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22851</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25732</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24716</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21155</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23715</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23979</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26779</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21811</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14197</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6279400000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.60387</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.64424</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57888</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.15688</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11729</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17694</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10604</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11611</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06717000000000001</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22544</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09866</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08878</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16846</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02764</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10739</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.11793</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13721</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02261</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.08948</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10322</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10144</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14133</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26053</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32301</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.57396</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.55796</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42235</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48016</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14273</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50376</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32832</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.62824</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.59037</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5106700000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.44808</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49618</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50639</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46923</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48934</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.6207999999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.49792</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.16294</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36761</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48185</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47296</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.56984</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.5263099999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.47463</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43986</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5869099999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52679</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55318</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47269</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5183300000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70192</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86954</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.58458</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5839500000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44211</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37239</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22794</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27811</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.18159</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16215</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07587000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.22922</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.2207</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17635</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26704</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17288</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06602</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06057999999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08070000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17744</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08787</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06307</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17979</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16221</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24369</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24987</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42816</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35936</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8653099999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42454</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25636</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24901</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11433</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.24344</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26151</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.7355499999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04868</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02036</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.24569</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23818</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.10965</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.09515</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49884</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42284</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.58109</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3592</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6159</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25774</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.2301</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14388</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20565</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22925</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11414</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1501</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00195</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04659000000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04694</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07847</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03008</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06302000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09669</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17009</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19561</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12034</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25435</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22923</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12391</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05537</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14613</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11725</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23643</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18476</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23603</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24296</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20306</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27534</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46724</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36585</v>
       </c>
     </row>
   </sheetData>
